--- a/data/base_datos_tincion.xlsx
+++ b/data/base_datos_tincion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fvygh\Documents\TESIS_PREGRADO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fvygh\Documents\TESIS_PREGRADO\TESIS-DE-PREGRADO\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864ABF8B-927C-435A-BE6B-08B3ED2F3F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3076EC9A-4853-4AF1-B901-DB7CF36DDA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="Hoja 2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>

--- a/data/base_datos_tincion.xlsx
+++ b/data/base_datos_tincion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fvygh\Documents\TESIS_PREGRADO\TESIS-DE-PREGRADO\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3076EC9A-4853-4AF1-B901-DB7CF36DDA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FE456D-BA66-4EC5-AAC7-16F8C6E442AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
